--- a/EddiewareOpeningRangeSetup/EddiewareOpeningRangeSetup/Score_indicator_results_updated_fallback.xlsx
+++ b/EddiewareOpeningRangeSetup/EddiewareOpeningRangeSetup/Score_indicator_results_updated_fallback.xlsx
@@ -463,11 +463,11 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <f>IF((COUNTIF(Q4:Q8,"&gt;0")+COUNTIF(Q4:Q8,"&lt;0"))=0,"",COUNTIF(Q4:Q8,"&gt;0")/(COUNTIF(Q4:Q8,"&gt;0")+COUNTIF(Q4:Q8,"&lt;0")))</f>
+        <f>IF((COUNTIF(Q4:Q4,"&gt;0")+COUNTIF(Q4:Q4,"&lt;0"))=0,"",COUNTIF(Q4:Q4,"&gt;0")/(COUNTIF(Q4:Q4,"&gt;0")+COUNTIF(Q4:Q4,"&lt;0")))</f>
         <v/>
       </c>
       <c r="B2" s="2">
-        <f>IF(ABS(SUMIF(Q4:Q8,"&lt;0",Q4:Q8))=0,IF(SUMIF(Q4:Q8,"&gt;0",Q4:Q8)&gt;0,"INF",""),SUMIF(Q4:Q8,"&gt;0",Q4:Q8)/ABS(SUMIF(Q4:Q8,"&lt;0",Q4:Q8)))</f>
+        <f>IF(ABS(SUMIF(Q4:Q4,"&lt;0",Q4:Q4))=0,IF(SUMIF(Q4:Q4,"&gt;0",Q4:Q4)&gt;0,"INF",""),SUMIF(Q4:Q4,"&gt;0",Q4:Q4)/ABS(SUMIF(Q4:Q4,"&lt;0",Q4:Q4)))</f>
         <v/>
       </c>
     </row>
@@ -651,29 +651,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29282.5</v>
+        <v>29241.25</v>
       </c>
       <c r="C4" t="n">
-        <v>29346.25</v>
+        <v>29291.25</v>
       </c>
       <c r="D4" t="n">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="E4" t="n">
-        <v>29316.27</v>
+        <v>29294.95</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>120</v>
+        <v>418</v>
       </c>
       <c r="H4" t="n">
-        <v>26</v>
+        <v>-178</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15.21</v>
+        <v>6.65</v>
       </c>
       <c r="K4" t="n">
         <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>29323.75</v>
+        <v>29262.5</v>
       </c>
       <c r="M4" t="n">
-        <v>29348.75</v>
+        <v>29237.5</v>
       </c>
       <c r="N4" t="n">
-        <v>29378.75</v>
+        <v>29207.5</v>
       </c>
       <c r="O4" t="n">
         <v>100</v>
@@ -706,19 +706,19 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="T4" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="U4" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>2311</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6576</v>
+        <v>2.2549</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -788,560 +788,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>29146.25</v>
-      </c>
-      <c r="C5" t="n">
-        <v>29227.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>325</v>
-      </c>
-      <c r="E5" t="n">
-        <v>29202.57</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" t="n">
-        <v>44</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>A+ speed</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>23.77</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>29205</v>
-      </c>
-      <c r="M5" t="n">
-        <v>29230</v>
-      </c>
-      <c r="N5" t="n">
-        <v>29260</v>
-      </c>
-      <c r="O5" t="n">
-        <v>100</v>
-      </c>
-      <c r="P5" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="T5" t="n">
-        <v>65</v>
-      </c>
-      <c r="U5" t="n">
-        <v>120</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>score-exporter-2026-05-22-sync-visual-speed</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>09:40:00</t>
-        </is>
-      </c>
-      <c r="X5" t="n">
-        <v>2320</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.4207</v>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>LastTime</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
+      <c r="Q5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>29252.5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>29288.75</v>
-      </c>
-      <c r="D6" t="n">
-        <v>145</v>
-      </c>
-      <c r="E6" t="n">
-        <v>29321.36</v>
-      </c>
-      <c r="F6" t="n">
-        <v>35</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1113</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-175</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>normal speed</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>29258.75</v>
-      </c>
-      <c r="M6" t="n">
-        <v>29243.75</v>
-      </c>
-      <c r="N6" t="n">
-        <v>29213.75</v>
-      </c>
-      <c r="O6" t="n">
-        <v>60</v>
-      </c>
-      <c r="P6" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>-60</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>SELL1</t>
-        </is>
-      </c>
-      <c r="T6" t="n">
-        <v>100</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>score-exporter-2026-05-22-sync-visual-speed</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>09:31:00</t>
-        </is>
-      </c>
-      <c r="X6" t="n">
-        <v>2311</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>16.8109</v>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>LastTime</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
+      <c r="Q6" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>29460</v>
-      </c>
-      <c r="C7" t="n">
-        <v>29492.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>130</v>
-      </c>
-      <c r="E7" t="n">
-        <v>29543.51</v>
-      </c>
-      <c r="F7" t="n">
-        <v>65</v>
-      </c>
-      <c r="G7" t="n">
-        <v>801</v>
-      </c>
-      <c r="H7" t="n">
-        <v>263</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>A+ speed</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>11.01</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>29490</v>
-      </c>
-      <c r="M7" t="n">
-        <v>29515</v>
-      </c>
-      <c r="N7" t="n">
-        <v>29545</v>
-      </c>
-      <c r="O7" t="n">
-        <v>100</v>
-      </c>
-      <c r="P7" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="T7" t="n">
-        <v>65</v>
-      </c>
-      <c r="U7" t="n">
-        <v>120</v>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>score-exporter-2026-05-22-sync-visual-speed</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>09:32:00</t>
-        </is>
-      </c>
-      <c r="X7" t="n">
-        <v>2312</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>5.9038</v>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>LastTime</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
+      <c r="Q7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>29241.25</v>
-      </c>
-      <c r="C8" t="n">
-        <v>29291.25</v>
-      </c>
-      <c r="D8" t="n">
-        <v>200</v>
-      </c>
-      <c r="E8" t="n">
-        <v>29294.95</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>404</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-174</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>normal speed</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>29253.75</v>
-      </c>
-      <c r="M8" t="n">
-        <v>29238.75</v>
-      </c>
-      <c r="N8" t="n">
-        <v>29208.75</v>
-      </c>
-      <c r="O8" t="n">
-        <v>60</v>
-      </c>
-      <c r="P8" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>-60</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>SELL1</t>
-        </is>
-      </c>
-      <c r="T8" t="n">
-        <v>80</v>
-      </c>
-      <c r="U8" t="n">
-        <v>15</v>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>score-exporter-2026-05-22-sync-visual-speed</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>09:31:00</t>
-        </is>
-      </c>
-      <c r="X8" t="n">
-        <v>2311</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.1714</v>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>LastTime</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
+      <c r="Q8" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/EddiewareOpeningRangeSetup/EddiewareOpeningRangeSetup/Score_indicator_results_updated_fallback.xlsx
+++ b/EddiewareOpeningRangeSetup/EddiewareOpeningRangeSetup/Score_indicator_results_updated_fallback.xlsx
@@ -463,11 +463,11 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <f>IF((COUNTIF(Q4:Q6,"&gt;0")+COUNTIF(Q4:Q6,"&lt;0"))=0,"",COUNTIF(Q4:Q6,"&gt;0")/(COUNTIF(Q4:Q6,"&gt;0")+COUNTIF(Q4:Q6,"&lt;0")))</f>
+        <f>IF((COUNTIF(Q4:Q4,"&gt;0")+COUNTIF(Q4:Q4,"&lt;0"))=0,"",COUNTIF(Q4:Q4,"&gt;0")/(COUNTIF(Q4:Q4,"&gt;0")+COUNTIF(Q4:Q4,"&lt;0")))</f>
         <v/>
       </c>
       <c r="B2" s="2">
-        <f>IF(ABS(SUMIF(Q4:Q6,"&lt;0",Q4:Q6))=0,IF(SUMIF(Q4:Q6,"&gt;0",Q4:Q6)&gt;0,"INF",""),SUMIF(Q4:Q6,"&gt;0",Q4:Q6)/ABS(SUMIF(Q4:Q6,"&lt;0",Q4:Q6)))</f>
+        <f>IF(ABS(SUMIF(Q4:Q4,"&lt;0",Q4:Q4))=0,IF(SUMIF(Q4:Q4,"&gt;0",Q4:Q4)&gt;0,"INF",""),SUMIF(Q4:Q4,"&gt;0",Q4:Q4)/ABS(SUMIF(Q4:Q4,"&lt;0",Q4:Q4)))</f>
         <v/>
       </c>
     </row>
@@ -656,29 +656,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29252.5</v>
+        <v>29241.25</v>
       </c>
       <c r="C4" t="n">
-        <v>29288.75</v>
+        <v>29291.25</v>
       </c>
       <c r="D4" t="n">
-        <v>145</v>
+        <v>200</v>
       </c>
       <c r="E4" t="n">
-        <v>29321.36</v>
+        <v>29294.95</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>1113</v>
+        <v>410</v>
       </c>
       <c r="H4" t="n">
-        <v>-175</v>
+        <v>-176</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -686,19 +686,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>29258.75</v>
+        <v>29255</v>
       </c>
       <c r="M4" t="n">
-        <v>29243.75</v>
+        <v>29240</v>
       </c>
       <c r="N4" t="n">
-        <v>29213.75</v>
+        <v>29210</v>
       </c>
       <c r="O4" t="n">
         <v>60</v>
@@ -707,7 +707,7 @@
         <v>120</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>25</v>
+        <v>22.5</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -723,11 +723,11 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>score-exporter-2026-05-25-fast-exit-close-price</t>
+          <t>score-exporter-2026-05-25-fast-exit-half-mfe</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -739,7 +739,7 @@
         <v>2311</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.8109</v>
+        <v>2.1962</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -758,326 +758,48 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>29237.5</v>
+        <v>29234.38</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>29460</v>
-      </c>
-      <c r="C5" t="n">
-        <v>29492.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>130</v>
-      </c>
-      <c r="E5" t="n">
-        <v>29543.51</v>
-      </c>
-      <c r="F5" t="n">
-        <v>65</v>
-      </c>
-      <c r="G5" t="n">
-        <v>802</v>
-      </c>
-      <c r="H5" t="n">
-        <v>262</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>A+ speed</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>10.97</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>29490</v>
-      </c>
-      <c r="M5" t="n">
-        <v>29515</v>
-      </c>
-      <c r="N5" t="n">
-        <v>29545</v>
-      </c>
-      <c r="O5" t="n">
-        <v>100</v>
-      </c>
-      <c r="P5" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="T5" t="n">
-        <v>25</v>
-      </c>
-      <c r="U5" t="n">
-        <v>120</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>score-exporter-2026-05-25-fast-exit-close-price</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>09:32:00</t>
-        </is>
-      </c>
-      <c r="X5" t="n">
-        <v>2312</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>5.9247</v>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>LastTime</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>29545</v>
-      </c>
+      <c r="Q5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>29241.25</v>
-      </c>
-      <c r="C6" t="n">
-        <v>29291.25</v>
-      </c>
-      <c r="D6" t="n">
-        <v>200</v>
-      </c>
-      <c r="E6" t="n">
-        <v>29294.95</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>404</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-174</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>normal speed</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>29253.75</v>
-      </c>
-      <c r="M6" t="n">
-        <v>29238.75</v>
-      </c>
-      <c r="N6" t="n">
-        <v>29208.75</v>
-      </c>
-      <c r="O6" t="n">
-        <v>60</v>
-      </c>
-      <c r="P6" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>SELL1</t>
-        </is>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>20</v>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>score-exporter-2026-05-25-fast-exit-close-price</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>09:31:00</t>
-        </is>
-      </c>
-      <c r="X6" t="n">
-        <v>2311</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.1714</v>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>LastTime</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>29236.25</v>
-      </c>
+      <c r="Q6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="Q7" s="4" t="n"/>

--- a/EddiewareOpeningRangeSetup/EddiewareOpeningRangeSetup/Score_indicator_results_updated_fallback.xlsx
+++ b/EddiewareOpeningRangeSetup/EddiewareOpeningRangeSetup/Score_indicator_results_updated_fallback.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AO25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -463,11 +463,11 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <f>IF((COUNTIF(R4:R6,"&gt;0")+COUNTIF(R4:R6,"&lt;0"))=0,"",COUNTIF(R4:R6,"&gt;0")/(COUNTIF(R4:R6,"&gt;0")+COUNTIF(R4:R6,"&lt;0")))</f>
+        <f>IF((COUNTIF(R4:R4,"&gt;0")+COUNTIF(R4:R4,"&lt;0"))=0,"",COUNTIF(R4:R4,"&gt;0")/(COUNTIF(R4:R4,"&gt;0")+COUNTIF(R4:R4,"&lt;0")))</f>
         <v/>
       </c>
       <c r="B2" s="2">
-        <f>IF(ABS(SUMIF(R4:R6,"&lt;0",R4:R6))=0,IF(SUMIF(R4:R6,"&gt;0",R4:R6)&gt;0,"INF",""),SUMIF(R4:R6,"&gt;0",R4:R6)/ABS(SUMIF(R4:R6,"&lt;0",R4:R6)))</f>
+        <f>IF(ABS(SUMIF(R4:R4,"&lt;0",R4:R4))=0,IF(SUMIF(R4:R4,"&gt;0",R4:R4)&gt;0,"INF",""),SUMIF(R4:R4,"&gt;0",R4:R4)/ABS(SUMIF(R4:R4,"&lt;0",R4:R4)))</f>
         <v/>
       </c>
     </row>
@@ -652,42 +652,257 @@
           <t>Result_Label</t>
         </is>
       </c>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t>APlus_Structure</t>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Imbalance_Group_3</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Imbalance_Group_Price</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>Imbalance_Count</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>Speed_Ignored_By_Structure</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>NO_TRADE</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>26852.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>26893.75</v>
+      </c>
+      <c r="D4" t="n">
+        <v>165</v>
+      </c>
+      <c r="E4" t="n">
+        <v>26841.85</v>
+      </c>
+      <c r="F4" t="n">
+        <v>70</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1313</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-117</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>normal speed</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26836.25</v>
+      </c>
+      <c r="M4" t="n">
+        <v>26821.25</v>
+      </c>
+      <c r="N4" t="n">
+        <v>26806.25</v>
+      </c>
+      <c r="O4" t="n">
+        <v>60</v>
+      </c>
+      <c r="P4" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>26836.25</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>-60</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>SCALP_NORMAL</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>65</v>
+      </c>
+      <c r="V4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>score-exporter-2026-05-30-aplus-structure-export</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>09:33:00</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>2312</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>33.3476</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>LastTime</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>26876.25</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="R5" s="4" t="inlineStr">
-        <is>
-          <t>NO_TRADE</t>
-        </is>
-      </c>
+      <c r="R5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>NO_TRADE</t>
-        </is>
-      </c>
+      <c r="R6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="R7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="R8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="R9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="R10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="R11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="R12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="R13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="R14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="R15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="R16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="R17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="R18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="R19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="R20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="R21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="R22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="R23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="R24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="R25" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
